--- a/data/excel/综合数据.xlsx
+++ b/data/excel/综合数据.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="113">
   <si>
     <t>品牌</t>
   </si>
@@ -320,6 +320,21 @@
   </si>
   <si>
     <t>海狮05EV</t>
+  </si>
+  <si>
+    <t>问界M7</t>
+  </si>
+  <si>
+    <t>轩逸</t>
+  </si>
+  <si>
+    <t>长安CS75 PLUS</t>
+  </si>
+  <si>
+    <t>Model 3</t>
+  </si>
+  <si>
+    <t>问界M6</t>
   </si>
   <si>
     <t>纯电动</t>
@@ -695,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U51"/>
+  <dimension ref="A1:U56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -777,10 +792,10 @@
         <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G2">
         <v>2024</v>
@@ -836,10 +851,10 @@
         <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G3">
         <v>2024</v>
@@ -895,10 +910,10 @@
         <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G4">
         <v>2024</v>
@@ -954,10 +969,10 @@
         <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G5">
         <v>2024</v>
@@ -1013,10 +1028,10 @@
         <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G6">
         <v>2024</v>
@@ -1072,10 +1087,10 @@
         <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G7">
         <v>2024</v>
@@ -1134,10 +1149,10 @@
         <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G8">
         <v>2024</v>
@@ -1196,10 +1211,10 @@
         <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G9">
         <v>2024</v>
@@ -1255,10 +1270,10 @@
         <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G10">
         <v>2024</v>
@@ -1314,10 +1329,10 @@
         <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G11">
         <v>2024</v>
@@ -1376,10 +1391,10 @@
         <v>62</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G12">
         <v>2024</v>
@@ -1435,10 +1450,10 @@
         <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G13">
         <v>2024</v>
@@ -1494,10 +1509,10 @@
         <v>64</v>
       </c>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F14" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G14">
         <v>2024</v>
@@ -1553,10 +1568,10 @@
         <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G15">
         <v>2024</v>
@@ -1612,10 +1627,10 @@
         <v>66</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G16">
         <v>2024</v>
@@ -1671,10 +1686,10 @@
         <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G17">
         <v>2024</v>
@@ -1730,10 +1745,10 @@
         <v>68</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F18" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G18">
         <v>2024</v>
@@ -1789,10 +1804,10 @@
         <v>69</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F19" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G19">
         <v>2024</v>
@@ -1848,10 +1863,10 @@
         <v>70</v>
       </c>
       <c r="E20" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F20" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G20">
         <v>2024</v>
@@ -1907,10 +1922,10 @@
         <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F21" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G21">
         <v>2024</v>
@@ -1969,10 +1984,10 @@
         <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F22" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G22">
         <v>2024</v>
@@ -2028,10 +2043,10 @@
         <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G23">
         <v>2024</v>
@@ -2087,10 +2102,10 @@
         <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F24" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G24">
         <v>2024</v>
@@ -2146,10 +2161,10 @@
         <v>75</v>
       </c>
       <c r="E25" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G25">
         <v>2024</v>
@@ -2205,10 +2220,10 @@
         <v>76</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F26" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G26">
         <v>2024</v>
@@ -2264,10 +2279,10 @@
         <v>77</v>
       </c>
       <c r="E27" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F27" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G27">
         <v>2024</v>
@@ -2323,10 +2338,10 @@
         <v>78</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F28" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G28">
         <v>2024</v>
@@ -2382,10 +2397,10 @@
         <v>79</v>
       </c>
       <c r="E29" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F29" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G29">
         <v>2024</v>
@@ -2441,10 +2456,10 @@
         <v>80</v>
       </c>
       <c r="E30" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G30">
         <v>2024</v>
@@ -2500,10 +2515,10 @@
         <v>81</v>
       </c>
       <c r="E31" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F31" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G31">
         <v>2024</v>
@@ -2559,10 +2574,10 @@
         <v>82</v>
       </c>
       <c r="E32" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F32" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G32">
         <v>2024</v>
@@ -2618,10 +2633,10 @@
         <v>83</v>
       </c>
       <c r="E33" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F33" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G33">
         <v>2024</v>
@@ -2677,10 +2692,10 @@
         <v>84</v>
       </c>
       <c r="E34" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F34" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G34">
         <v>2024</v>
@@ -2736,10 +2751,10 @@
         <v>85</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F35" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G35">
         <v>2024</v>
@@ -2795,10 +2810,10 @@
         <v>86</v>
       </c>
       <c r="E36" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F36" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G36">
         <v>2024</v>
@@ -2854,10 +2869,10 @@
         <v>87</v>
       </c>
       <c r="E37" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F37" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G37">
         <v>2024</v>
@@ -2913,10 +2928,10 @@
         <v>88</v>
       </c>
       <c r="E38" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F38" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G38">
         <v>2024</v>
@@ -2972,10 +2987,10 @@
         <v>89</v>
       </c>
       <c r="E39" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F39" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G39">
         <v>2024</v>
@@ -3031,10 +3046,10 @@
         <v>90</v>
       </c>
       <c r="E40" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F40" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G40">
         <v>2024</v>
@@ -3090,10 +3105,10 @@
         <v>91</v>
       </c>
       <c r="E41" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F41" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G41">
         <v>2024</v>
@@ -3149,10 +3164,10 @@
         <v>92</v>
       </c>
       <c r="E42" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F42" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G42">
         <v>2024</v>
@@ -3208,10 +3223,10 @@
         <v>93</v>
       </c>
       <c r="E43" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F43" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G43">
         <v>2024</v>
@@ -3267,10 +3282,10 @@
         <v>94</v>
       </c>
       <c r="E44" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F44" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G44">
         <v>2024</v>
@@ -3326,10 +3341,10 @@
         <v>95</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F45" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G45">
         <v>2024</v>
@@ -3385,10 +3400,10 @@
         <v>96</v>
       </c>
       <c r="E46" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F46" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G46">
         <v>2024</v>
@@ -3444,10 +3459,10 @@
         <v>97</v>
       </c>
       <c r="E47" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F47" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G47">
         <v>2024</v>
@@ -3503,10 +3518,10 @@
         <v>98</v>
       </c>
       <c r="E48" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F48" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G48">
         <v>2024</v>
@@ -3562,10 +3577,10 @@
         <v>99</v>
       </c>
       <c r="E49" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F49" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G49">
         <v>2024</v>
@@ -3621,10 +3636,10 @@
         <v>100</v>
       </c>
       <c r="E50" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F50" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G50">
         <v>2024</v>
@@ -3680,10 +3695,10 @@
         <v>101</v>
       </c>
       <c r="E51" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F51" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G51">
         <v>2024</v>
@@ -3723,6 +3738,136 @@
       </c>
       <c r="T51">
         <v>4.6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
+      <c r="A52" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" t="s">
+        <v>102</v>
+      </c>
+      <c r="E52" t="s">
+        <v>108</v>
+      </c>
+      <c r="H52">
+        <v>27.98</v>
+      </c>
+      <c r="I52">
+        <v>38.98</v>
+      </c>
+      <c r="J52">
+        <v>33.48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
+      <c r="A53" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53" t="s">
+        <v>51</v>
+      </c>
+      <c r="D53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E53" t="s">
+        <v>108</v>
+      </c>
+      <c r="H53">
+        <v>6.19</v>
+      </c>
+      <c r="I53">
+        <v>14.19</v>
+      </c>
+      <c r="J53">
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20">
+      <c r="A54" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54" t="s">
+        <v>104</v>
+      </c>
+      <c r="E54" t="s">
+        <v>108</v>
+      </c>
+      <c r="H54">
+        <v>9.19</v>
+      </c>
+      <c r="I54">
+        <v>13.59</v>
+      </c>
+      <c r="J54">
+        <v>11.39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20">
+      <c r="A55" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" t="s">
+        <v>47</v>
+      </c>
+      <c r="C55" t="s">
+        <v>51</v>
+      </c>
+      <c r="D55" t="s">
+        <v>105</v>
+      </c>
+      <c r="E55" t="s">
+        <v>108</v>
+      </c>
+      <c r="H55">
+        <v>23.55</v>
+      </c>
+      <c r="I55">
+        <v>33.95</v>
+      </c>
+      <c r="J55">
+        <v>28.75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
+      <c r="A56" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" t="s">
+        <v>51</v>
+      </c>
+      <c r="D56" t="s">
+        <v>106</v>
+      </c>
+      <c r="E56" t="s">
+        <v>108</v>
+      </c>
+      <c r="H56">
+        <v>22.98</v>
+      </c>
+      <c r="I56">
+        <v>29.98</v>
+      </c>
+      <c r="J56">
+        <v>26.48</v>
       </c>
     </row>
   </sheetData>
